--- a/Excel Assignment 2 - Data Cleaning and Transformation.xlsx
+++ b/Excel Assignment 2 - Data Cleaning and Transformation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreeh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC18E3CD-2110-4D11-B27C-22A8E596A1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122C4A2E-AB42-432D-9A7C-F85264817541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="99">
   <si>
     <t>Perform the following in the dataset from the 'Dataset' sheet.</t>
   </si>
@@ -286,9 +286,6 @@
   </si>
   <si>
     <t>Casio</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>US</t>
@@ -469,12 +466,9 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor theme="7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1929,10 +1923,10 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>19</v>
@@ -1950,7 +1944,7 @@
         <v>23</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1958,7 +1952,7 @@
         <v>46050</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>24</v>
@@ -1985,7 +1979,7 @@
         <v>46068</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -2020,7 +2014,7 @@
         <v>46084</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>30</v>
@@ -2055,7 +2049,7 @@
         <v>46123</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>33</v>
@@ -2090,7 +2084,7 @@
         <v>46164</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>35</v>
@@ -2117,7 +2111,7 @@
         <v>46180</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>37</v>
@@ -2144,7 +2138,7 @@
         <v>46222</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>39</v>
@@ -2171,7 +2165,7 @@
         <v>46257</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>41</v>
@@ -2198,7 +2192,7 @@
         <v>46270</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>43</v>
@@ -2225,7 +2219,7 @@
         <v>46309</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>45</v>
@@ -2252,7 +2246,7 @@
         <v>46190</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>48</v>
@@ -2279,7 +2273,7 @@
         <v>46351</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>27</v>
@@ -2306,7 +2300,7 @@
         <v>46364</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>30</v>
@@ -2321,7 +2315,7 @@
         <v>35</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -2333,7 +2327,7 @@
         <v>46071</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>51</v>
@@ -2360,7 +2354,7 @@
         <v>46128</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>53</v>
@@ -2387,7 +2381,7 @@
         <v>46255</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>55</v>
@@ -2414,7 +2408,7 @@
         <v>46254</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>51</v>
@@ -2441,7 +2435,7 @@
         <v>46049</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>24</v>
@@ -2468,7 +2462,7 @@
         <v>46082</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>60</v>
@@ -2495,7 +2489,7 @@
         <v>46248</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>62</v>
@@ -2503,8 +2497,9 @@
       <c r="D21" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>83</v>
+      <c r="E21" s="11">
+        <f ca="1">AVERAGE(E2:E32)</f>
+        <v>0</v>
       </c>
       <c r="F21" s="8">
         <v>10</v>
@@ -2522,7 +2517,7 @@
         <v>46156</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>64</v>
@@ -2549,7 +2544,7 @@
         <v>46031</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>66</v>
@@ -2576,7 +2571,7 @@
         <v>46222</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>68</v>
@@ -2603,7 +2598,7 @@
         <v>46294</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>70</v>
@@ -2630,7 +2625,7 @@
         <v>46176</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>60</v>
@@ -2657,7 +2652,7 @@
         <v>46214</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>41</v>
@@ -2684,7 +2679,7 @@
         <v>46088</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>74</v>
@@ -2711,7 +2706,7 @@
         <v>46125</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>76</v>
@@ -2738,7 +2733,7 @@
         <v>46166</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>68</v>
@@ -2765,7 +2760,7 @@
         <v>46358</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>79</v>
@@ -2792,7 +2787,7 @@
         <v>46212</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>81</v>
@@ -3783,8 +3778,8 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="dataBar" priority="2">
+  <conditionalFormatting sqref="E33:E1048576">
+    <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3797,9 +3792,23 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Electronics">
-      <formula>NOT(ISERROR(SEARCH("Electronics",G1)))</formula>
+  <conditionalFormatting sqref="A2:H32">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>TRIM($G2)="Electronics"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9FAB59A6-3A84-4A2E-889B-DCC2B6E67F44}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3818,6 +3827,19 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
+          <xm:sqref>E33:E1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9FAB59A6-3A84-4A2E-889B-DCC2B6E67F44}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFFB628"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
           <xm:sqref>E1:E1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
